--- a/backend/analysis_report.xlsx
+++ b/backend/analysis_report.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H11"/>
+  <dimension ref="A1:H15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -446,7 +446,7 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>disease</t>
+          <t>health_issue</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
@@ -832,6 +832,158 @@
       </c>
       <c r="H11" t="n">
         <v>1</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>50</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Abuja</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Typhoid</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Fever;Headache</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H12" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>30</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Kano</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Cholera</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Vomiting;Diarrhea</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H13" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>34</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Ibadan</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Malaria</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Fever;Chills</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H14" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>22</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Lagos</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Typhoid</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Fever;Headache</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H15" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/backend/analysis_report.xlsx
+++ b/backend/analysis_report.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H15"/>
+  <dimension ref="A1:H30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -912,7 +912,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
@@ -931,12 +931,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Fever;Chills</t>
+          <t>Fever;Headache</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -950,7 +950,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
@@ -974,15 +974,561 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
+          <t>Fever;Cough</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>36</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Abuja</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>59</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Enugu</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Malaria</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Fever;Sweating</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H17" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>19</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Kaduna</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Typhoid</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Fever;Vomiting</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H18" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>32</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Lagos</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Malaria</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Fever;Fatigue</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H19" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>46</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Port Harcourt</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Cholera</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Diarrhea;Cramps</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H20" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>61</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Ibadan</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>40</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Abuja</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Malaria</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Fever;Chills</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H22" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>21</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Kano</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Typhoid</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Fever;Stomach Pain</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H23" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>33</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Lagos</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Malaria</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Fever;Fatigue</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H24" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>57</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Enugu</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Cholera</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Diarrhea;Vomiting</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H25" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>35</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Kaduna</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr"/>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H26" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>43</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Ibadan</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Malaria</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Fever;Cough</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H27" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>28</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Lagos</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Typhoid</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
           <t>Fever;Headache</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H15" t="n">
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H28" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>39</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Abuja</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Cholera</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Vomiting;Diarrhea</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H29" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>24</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Kano</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Malaria</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Fever;Sweating</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H30" t="n">
         <v>0</v>
       </c>
     </row>

--- a/backend/analysis_report.xlsx
+++ b/backend/analysis_report.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H30"/>
+  <dimension ref="A1:H11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -446,7 +446,7 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>health_issue</t>
+          <t>disease</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
@@ -832,704 +832,6 @@
       </c>
       <c r="H11" t="n">
         <v>1</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>50</v>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Abuja</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Typhoid</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>Fever;Headache</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H12" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>30</v>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Kano</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Cholera</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>Vomiting;Diarrhea</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H13" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>44</v>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ibadan</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>Malaria</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>Fever;Headache</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H14" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>23</v>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Lagos</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>Typhoid</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>Fever;Cough</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H15" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>36</v>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Abuja</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H16" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>59</v>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Enugu</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>Malaria</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>Fever;Sweating</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H17" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>19</v>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Kaduna</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>Typhoid</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>Fever;Vomiting</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H18" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>32</v>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Lagos</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>Malaria</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>Fever;Fatigue</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H19" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>46</v>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Port Harcourt</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>Cholera</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>Diarrhea;Cramps</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H20" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>61</v>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ibadan</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr"/>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H21" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>40</v>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Abuja</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>Malaria</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>Fever;Chills</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H22" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>21</v>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Kano</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>Typhoid</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>Fever;Stomach Pain</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H23" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
-        <v>33</v>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Lagos</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>Malaria</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>Fever;Fatigue</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H24" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="n">
-        <v>57</v>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Enugu</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>Cholera</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>Diarrhea;Vomiting</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H25" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="n">
-        <v>35</v>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Kaduna</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr"/>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H26" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="n">
-        <v>43</v>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ibadan</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>Malaria</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>Fever;Cough</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H27" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="n">
-        <v>28</v>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Lagos</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>Typhoid</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>Fever;Headache</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H28" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="n">
-        <v>39</v>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Abuja</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>Cholera</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>Vomiting;Diarrhea</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H29" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="n">
-        <v>24</v>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Kano</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>Malaria</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>Fever;Sweating</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H30" t="n">
-        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/backend/analysis_report.xlsx
+++ b/backend/analysis_report.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H11"/>
+  <dimension ref="A1:H30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -834,6 +834,704 @@
         <v>1</v>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>50</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Abuja</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Typhoid</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Fever;Headache</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H12" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>30</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Kano</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Cholera</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Vomiting;Diarrhea</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H13" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>44</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Ibadan</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Malaria</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Fever;Headache</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H14" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>23</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Lagos</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Typhoid</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Fever;Cough</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>36</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Abuja</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>59</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Enugu</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Malaria</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Fever;Sweating</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H17" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>19</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Kaduna</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Typhoid</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Fever;Vomiting</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H18" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>32</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Lagos</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Malaria</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Fever;Fatigue</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H19" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>46</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Port Harcourt</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Cholera</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Diarrhea;Cramps</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H20" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>61</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Ibadan</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>40</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Abuja</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Malaria</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Fever;Chills</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H22" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>21</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Kano</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Typhoid</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Fever;Stomach Pain</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H23" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>33</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Lagos</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Malaria</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Fever;Fatigue</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H24" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>57</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Enugu</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Cholera</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Diarrhea;Vomiting</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H25" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>35</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Kaduna</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr"/>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H26" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>43</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Ibadan</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Malaria</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Fever;Cough</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H27" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>28</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Lagos</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Typhoid</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Fever;Headache</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H28" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>39</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Abuja</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Cholera</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Vomiting;Diarrhea</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H29" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>24</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Kano</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Malaria</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Fever;Sweating</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H30" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
